--- a/MyJournalApp/wwwroot/group-files/Б2-22_sem1.xlsx
+++ b/MyJournalApp/wwwroot/group-files/Б2-22_sem1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! Секретар навчальної частини\Секретар\Індивідуальні плани\2025-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B61DD93-DB8C-49F7-8071-9B658600AA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>ІНДИВІДУАЛЬНИЙ НАВЧАЛЬНИЙ ПЛАН</t>
   </si>
@@ -40,6 +39,9 @@
   </si>
   <si>
     <t>Будівництво та цивільна інженерія</t>
+  </si>
+  <si>
+    <t>1 півріччя</t>
   </si>
   <si>
     <t>ПРЕДМЕТ</t>
@@ -136,61 +138,61 @@
     <t>іспит</t>
   </si>
   <si>
-    <t>захист КП/КР</t>
-  </si>
-  <si>
-    <t>Ремига О.О.</t>
-  </si>
-  <si>
-    <t>2 півріччя</t>
-  </si>
-  <si>
-    <t>захист ДП</t>
+    <t xml:space="preserve">Фізичне виховання                                                     </t>
   </si>
   <si>
     <t xml:space="preserve">Економіка будівництва                                                 </t>
   </si>
   <si>
-    <t>Маркін С.А.</t>
+    <t xml:space="preserve">Основи систем автоматизованого проектування                           </t>
+  </si>
+  <si>
+    <t>Технологія ремонтно-будівельних робіт</t>
+  </si>
+  <si>
+    <t>Технічна експлуатація будівель</t>
+  </si>
+  <si>
+    <t>Технологічна практика</t>
   </si>
   <si>
     <t>Іванова Г.О.</t>
   </si>
   <si>
+    <t>Капля С.В.</t>
+  </si>
+  <si>
     <t>Міхова А.К.</t>
   </si>
   <si>
-    <t>Індивідуальне житлове будівництво</t>
-  </si>
-  <si>
-    <t>Комп`ютерна графіка</t>
+    <t>Денисенко В.В.</t>
   </si>
   <si>
     <t>Пшегорлінська О.А.</t>
   </si>
   <si>
+    <t xml:space="preserve">Охорона праці в галузі    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медична безпека                                      </t>
+  </si>
+  <si>
+    <t>Карташев Д.Ю.</t>
+  </si>
+  <si>
+    <t>Куліш С.О.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Технологія і організація будівельного виробництва             </t>
   </si>
   <si>
-    <t xml:space="preserve">КП Технологія і організація будівельного виробництва             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР Економіка будівництва                                                 </t>
-  </si>
-  <si>
-    <t>Основи  ефективного  управління підприємством</t>
-  </si>
-  <si>
-    <t>Фізична культура</t>
-  </si>
-  <si>
-    <t>Фізичне виховання</t>
+    <t>Ціноутворення</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -297,7 +299,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -417,20 +419,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -459,31 +452,13 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -795,8 +770,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -806,186 +781,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+      <c r="A2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="24" t="s">
+      <c r="A4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
     </row>
     <row r="5" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="25" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
+      <c r="A7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" spans="1:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
     </row>
     <row r="10" spans="1:13" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="22"/>
+      <c r="A10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16"/>
     </row>
     <row r="11" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="L11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -993,14 +968,12 @@
         <v>1</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2">
-        <v>74</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="2">
         <v>16</v>
       </c>
@@ -1008,82 +981,80 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J12" s="2">
-        <v>180</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E13" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="J13" s="2">
-        <v>142</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>26</v>
+        <v>60</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M13" s="9"/>
     </row>
-    <row r="14" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="D14" s="2">
-        <v>22</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2">
+        <v>28</v>
+      </c>
+      <c r="J14" s="2">
+        <v>60</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="2">
-        <v>45</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="L14" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M14" s="9"/>
     </row>
@@ -1092,172 +1063,231 @@
         <v>4</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="2">
-        <v>50</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J15" s="2">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M15" s="9"/>
     </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>12</v>
+      </c>
       <c r="E16" s="2">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J16" s="2">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M16" s="9"/>
     </row>
-    <row r="17" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>6</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>40</v>
+      <c r="B17" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="C17" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2">
+        <v>16</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2">
+        <v>28</v>
+      </c>
       <c r="J17" s="2">
-        <v>20</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>27</v>
+        <v>60</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M17" s="9"/>
     </row>
-    <row r="18" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>7</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="13">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13">
-        <v>30</v>
-      </c>
-      <c r="K18" s="16" t="s">
+      <c r="C18" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D18" s="2">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2">
+        <v>43</v>
+      </c>
+      <c r="J18" s="2">
+        <v>75</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="14"/>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>8</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="15">
-        <v>6</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15">
-        <v>180</v>
+        <v>43</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" s="2">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2">
+        <v>14</v>
+      </c>
+      <c r="J19" s="2">
+        <v>38</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="18"/>
+        <v>15</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="9"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="16">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="2">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2">
+        <v>21</v>
+      </c>
+      <c r="J20" s="2">
+        <v>45</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>10</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2">
         <v>12</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="17"/>
-      <c r="M20" s="18"/>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2">
+        <v>360</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M21" s="9"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
